--- a/data_extactor/batch_10_fa/batch_0018_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0018_fa.xlsx
@@ -508,7 +508,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | صحبت کردن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -518,17 +518,17 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | بیان نوشتاری | حساسیت به مسئله | استدلال استقرایی | نظم‌دهی اطلاعات | درک شنیداری | درک نوشتاری | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | خلاقیت | دید نزدیک | وضوح گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | تشخیص گفتار | دید دور | توانایی عددی | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی</t>
+          <t>استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | اصالت | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | تشخیص گفتار | بینایی دور | توانایی عددی | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | تأثیر تصمیمات بر همکاران یا نتایج شرکت | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | کار با یا مشارکت در یک گروه کاری یا تیم | پیامد خطا | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های سرویس هواپیما | مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | مدیران معماری و مهندسی | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان صنایع | کارگران نگهداری و تعمیرات، عمومی | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مکانیک‌ها و تکنسین‌های سرویس قایق موتوری | مهندسان کشتی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک‌ها و تکنسین‌های خدمات هواپیما | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | مدیران معماری و مهندسی | تکنسین‌های مهندسی خودرو | تکنسین‌های هوانوردی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان صنایع | کارگران نگهداری و تعمیرات عمومی | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مکانیک‌ها و تکنسین‌های خدمات قایق‌های موتوری | مهندسان کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,12 +560,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ANSYS Multiphysics | Autodesk AutoCAD | C++ | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار همبستگی تصویر دیجیتال DIC | نرم‌افزار تشخیص، جداسازی و بازیابی خطا FDIR | نرم‌افزار تحلیل المان محدود | زبان برنامه‌نویسی FORTRAN | سیستم‌های نمونه‌سازی سریع مدل‌سازی رسوب ذوبی FDM | نرم‌افزار گرافیکی | IBM Notes | سیستم‌های تحلیل تصویر | MTS Testworks | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Database | PTC Creo Parametric | Python | QMC CM4D | نرم‌افزار SAP | سیستم‌های نمونه‌سازی سریع استریولیتوگرافی SLA | The MathWorks MATLAB | نرم‌افزار مرورگر وب</t>
+          <t>ANSYS Multiphysics | Autodesk AutoCAD | C++ | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار همبستگی تصویر دیجیتال DIC | نرم‌افزار تشخیص، جداسازی و بازیابی خطا FDIR | نرم‌افزار تحلیل المان محدود | Formula translation/translator FORTRAN | سیستم‌های نمونه‌سازی سریع مدل‌سازی رسوب ذوبی FDM | نرم‌افزار گرافیکی | IBM Notes | سیستم‌های تحلیل تصویر | MTS Testworks | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic.NET | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Database | PTC Creo Parametric | Python | QMC CM4D | نرم‌افزار SAP | سیستم‌های نمونه‌سازی سریع استریولیتوگرافی SLA | The MathWorks MATLAB | نرم‌افزار مرورگر وب</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علوم | گوش دادن فعال | درک مطلب | تفکر انتقادی | نوشتن | صحبت کردن | ریاضیات | یادگیری فعال | نظارت | استراتژی‌های یادگیری</t>
+          <t>علوم | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -575,17 +575,17 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان نوشتاری | حساسیت به مسئله | دید نزدیک | نظم‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | خلاقیت | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص گفتار | وضوح گفتار | توانایی عددی | توجه انتخابی | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص گفتار | وضوح گفتار | توانایی عددی | توجه انتخابی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارگران | نتایج کاری و خروجی‌های سایر کارگران | صرف زمان برای نشستن | فشار زمانی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | آزادی در تصمیم‌گیری | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | ارتباط با دیگران | سلامت و ایمنی سایر کارکنان | پیامدهای کاری و نتایج سایر کارکنان | صرف زمان برای نشستن | فشار زمانی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان پزشکی | مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | طراحان تجاری و صنعتی | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز رایانه | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنولوژیست‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک</t>
+          <t>مدیران معماری و مهندسی | مهندسان زیستی و مهندسان زیست‌پزشکی | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | طراحان تجاری و صنعتی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,12 +617,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | نرم‌افزار شبیه‌سازی ANSYS | نرم‌افزار تست عمر تسریع‌شده | Adobe ActionScript | Adobe Illustrator | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | نرم‌افزار صورت‌حساب مواد | Blink | Blue Ridge Numerics CFDesign | C | C++ | Chef | نرم‌افزار دینامیک سیالات محاسباتی CFD | نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه CADD | نرم‌افزار کنترل عددی رایانه‌ای CNC | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار طراحی آزمایش DOE | نرم‌افزار ESRI ArcGIS | نرم‌افزار ارزیابی خرابی | نرم‌افزار تحلیل حالت‌ها و اثرات خرابی FMEA | نرم‌افزار روش المان محدود FEM | G-code | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تولید شبکه | زبان گرافیکی Hewlett-Packard HPGL | نرم‌افزار رابط انسان و ماشین HMI | IBM Notes | InnovMetric PolyWorks | Intergraph Plant Design System PDS | Ladder Logic | Lambda Research OSLO | نرم‌افزار هزینه چرخه عمر | MAYA Nastran | MUMPS M | Mathsoft Mathcad | نرم‌افزار تولید مش | Metrix Imageware Surfacer | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | نرم‌افزار تحلیل مودال | نرم‌افزار تحلیل حرکت | National Instruments LabVIEW | نرم‌افزار تحلیل نوری | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | Puppet | Python | R | نرم‌افزار نمونه‌سازی سریع | ReliaSoft Alta 6 Pro | ReliaSoft BlockSim | ReliaSoft Weibull++ 6 | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار مهندسی معکوس | نرم‌افزار Rockwell Automation | نرم‌افزار SAP | Shell script | Sigmetrix CETOL 6 Sigma | SmugMug Flickr | SolidWorks COSMOSWorks | نرم‌افزار تحلیل انرژی آماری SEA | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | Teradata Database | The MathWorks MATLAB | Trimble SketchUp Pro | UGS I-DEAS | Verilog | نرم‌افزار تحلیل ویدیو | Zemax</t>
+          <t>1CadCam Unigraphics | نرم‌افزار شبیه‌سازی ANSYS | نرم‌افزار تست عمر تسریع‌شده | Adobe ActionScript | Adobe Illustrator | Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Autodesk Revit | Bentley MicroStation | نرم‌افزار صورت‌حساب مواد | Blink | Blue Ridge Numerics CFDesign | C | C++ | Chef | نرم‌افزار دینامیک سیالات محاسباتی CFD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار کنترل عددی کامپیوتری CNC | نرم‌افزار برآورد هزینه | Dassault Systemes CATIA | Dassault Systemes SolidWorks | نرم‌افزار جمع‌آوری داده | نرم‌افزار طراحی آزمایش‌ها DOE | نرم‌افزار ESRI ArcGIS | نرم‌افزار ارزیابی خرابی | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | نرم‌افزار روش المان محدود FEM | G-code | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | نرم‌افزار تولید شبکه | زبان گرافیکی Hewlett-Packard HPGL | نرم‌افزار رابط انسان و ماشین HMI | IBM Notes | InnovMetric PolyWorks | Intergraph Plant Design System PDS | Ladder Logic | Lambda Research OSLO | نرم‌افزار هزینه چرخه عمر | MAYA Nastran | MUMPS M | Mathsoft Mathcad | نرم‌افزار تولید مش | Metrix Imageware Surfacer | Microsoft Access | Microsoft Dynamics | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic for Applications VBA | Microsoft Word | Minitab | نرم‌افزار تحلیل مودال | نرم‌افزار تحلیل حرکت | National Instruments LabVIEW | نرم‌افزار تحلیل نوری | Oracle JD Edwards EnterpriseOne | Oracle Primavera Enterprise Project Portfolio Management | PTC Creo Parametric | نرم‌افزار Perforce Helix | Perl | Puppet | Python | R | نرم‌افزار نمونه‌سازی سریع | ReliaSoft Alta 6 Pro | ReliaSoft BlockSim | ReliaSoft Weibull++ 6 | نرم‌افزار تحلیل قابلیت اطمینان | نرم‌افزار مهندسی معکوس | نرم‌افزار Rockwell Automation | نرم‌افزار SAP | Shell script | Sigmetrix CETOL 6 Sigma | SmugMug Flickr | SolidWorks COSMOSWorks | نرم‌افزار تحلیل انرژی آماری SEA | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Teradata Database | The MathWorks MATLAB | Trimble SketchUp Pro | UGS I-DEAS | Verilog | نرم‌افزار تحلیل ویدیو | Zemax</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نوشتن | صحبت کردن | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -632,17 +632,17 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | نظم‌دهی اطلاعات | استدلال ریاضی | دید نزدیک | بیان نوشتاری | توانایی عددی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تجسم | خلاقیت | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | حافظه‌سپاری | توجه انتخابی | سرعت ادراکی</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | بیان کتبی | توانایی عددی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تجسم | اصالت | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | حفظ کردن | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل محیطی | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا صحیح بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | نتایج کاری و خروجی‌های سایر کارگران | سطح رقابت | فشار زمانی</t>
+          <t>ایمیل | ارتباط با دیگران | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | پیامدهای کاری و نتایج سایر کارکنان | سطح رقابت | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مونتاژکاران سازه، سطوح، تجهیزات و سیستم‌های هواپیما | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصاب‌ها و تعمیرکاران کنترل و شیرآلات، به جز درب مکانیکی | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز رایانه | مونتاژکاران موتور و سایر ماشین‌آلات | مهندسان پیل سوختی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | مهندسان ایستگاه و اپراتورهای دیگ بخار</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مونتاژکنندگان سازه، سطوح، تجهیزات و سیستم‌های هواپیما | مهندسان خودرو | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات، به جز درب‌های مکانیکی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مونتاژکنندگان تجهیزات الکتریکی و الکترونیکی | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | مهندسان پیل سوختی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکاترونیک | مهندسان تاسیسات و اپراتورهای دیگ بخار</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,12 +674,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ASPEN PLUS | Ansoft Simplorer | Ansys Fluent | Autodesk AutoCAD | C | C++ | FactSage | نرم‌افزار تحلیل حالت‌ها و اثرات خرابی FMEA | GE Energy GateCycle | Gaussian GaussView | نرم‌افزار Gaussian | IBM Cloud | Maplesoft Maple | MathWorks Simulink | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Database | Python | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و جمع‌آوری داده SCADA | The MathWorks MATLAB | Wind River Systems C/C++ Compiler Suite | Wolfram Research Mathematica</t>
+          <t>ASPEN PLUS | Ansoft Simplorer | Ansys Fluent | Autodesk AutoCAD | C | C++ | FactSage | نرم‌افزار تجزیه و تحلیل حالت‌های خرابی و اثرات آن FMEA | GE Energy GateCycle | Gaussian GaussView | نرم‌افزار Gaussian | IBM Cloud | Maplesoft Maple | MathWorks Simulink | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Windows | Microsoft Word | Minitab | National Instruments LabVIEW | Oracle Database | Python | نرم‌افزار آماری | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | The MathWorks MATLAB | Wind River Systems C/C++ Compiler Suite | Wolfram Research Mathematica</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم | نوشتن | صحبت کردن | گوش دادن فعال | یادگیری فعال | نظارت | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,17 +689,17 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | درک نوشتاری | بیان شفاهی | استدلال ریاضی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | دید نزدیک | روانی ایده‌ها | خلاقیت | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | تجسم | دید دور | وضوح گفتار | سرعت بستار | سرعت ادراکی</t>
+          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | تجسم | بینایی دور | وضوح گفتار | سرعت بستار | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارگران | قرار گرفتن در معرض شرایط خطرناک</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | مکالمات تلفنی | اهمیت دقیق یا درست بودن | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | سلامت و ایمنی سایر کارکنان | قرار گرفتن در معرض شرایط خطرناک</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | مدیران فناوری سوخت‌های زیستی/بیودیزل و توسعه محصول | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تکنولوژیست‌ها و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز رایانه | مهندسان انرژی، به جز باد و خورشید | دانشمندان مواد | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | مهندسان هسته‌ای | مهندسان سیستم‌های انرژی خورشیدی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تکنسین‌ها و کارشناسان الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان انرژی، به جز باد و خورشید | دانشمندان مواد | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان نانوسیستم | مهندسان هسته‌ای | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1CadCam Unigraphics | نرم‌افزار شبیه‌سازی ANSYS | AVL AVL CRUISE | Adobe Photoshop | Altair Engineering MotionSolve | Ambient Design ArtRage | Ansys Fluent | Apache Groovy | Ashlar-Vellum Graphite | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Alias Automotive | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | Autodesk Inventor | Autodesk SketchBook Pro | C | C# | C++ | CADRE Analytic | CNC Mastercam | Corel Painter | Corel Painter Sketch Pad | Dassault Systemes CATIA | Dassault Systemes Simulia Abaqus FEA | Dassault Systemes SolidWorks | سیستم‌های جمع‌آوری داده | نرم‌افزار دیباگ | Digital Equipment Corporation DIGITAL Fortran 90 | زبان نشانه‌گذاری توسعه‌پذیر XML | GNU Image Manipulation Program GIMP | Gamma Technologies GT-SUITE | Git | نرم‌افزار شبیه‌سازی سخت‌افزار در حلقه HIL | IBM Notes | International Material Data System IMDS | IronCAD | JUnit | JavaScript | JavaScript Object Notation JSON | Jenkins CI | LMS Imagine.Lab AMESim | Linux | MAHLE Powertrain | Magellan Firmware | Maplesoft Maple | Maplesoft MapleSim | MathWorks Simulink | Mentor Graphics Flowmaster | Metrologic Group Metrolog XG | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | Node.js | نرم‌افزار محیط توسعه شیءگرا | Oracle Java | PTC Creo Parametric | Perl | Portalgraphics openCanvas | Python | نرم‌افزار SAP | نرم‌افزار Salesforce | Selenium | Siemens NX | Siemens Solid Edge | Siemens Teamcenter | Somat eDAQ | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | Swift | SystemVerilog | TestNG | The MathWorks MATLAB | Think3 ThinkDesign Engineering | UNIX | زبان توصیف سخت‌افزار VHSIC بسیار سریع VHDL | Xcode</t>
+          <t>1CadCam Unigraphics | نرم‌افزار شبیه‌سازی ANSYS | AVL AVL CRUISE | Adobe Photoshop | Altair Engineering MotionSolve | Ambient Design ArtRage | Ansys Fluent | Apache Groovy | Ashlar-Vellum Graphite | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Autodesk Alias Automotive | Autodesk AutoCAD | Autodesk AutoCAD Mechanical | Autodesk Inventor | Autodesk SketchBook Pro | C | C# | C++ | CADRE Analytic | CNC Mastercam | Corel Painter | Corel Painter Sketch Pad | Dassault Systemes CATIA | Dassault Systemes Simulia Abaqus FEA | Dassault Systemes SolidWorks | سیستم‌های جمع‌آوری داده | نرم‌افزار عیب‌یابی | Digital Equipment Corporation DIGITAL Fortran 90 | زبان نشانه‌گذاری توسعه‌پذیر XML | برنامه دستکاری تصویر گنو GIMP | Gamma Technologies GT-SUITE | Git | نرم‌افزار شبیه‌سازی سخت‌افزار در حلقه HIL | IBM Notes | International Material Data System IMDS | IronCAD | JUnit | JavaScript | JavaScript Object Notation JSON | Jenkins CI | LMS Imagine.Lab AMESim | Linux | MAHLE Powertrain | Magellan Firmware | Maplesoft Maple | Maplesoft MapleSim | MathWorks Simulink | Mentor Graphics Flowmaster | Metrologic Group Metrolog XG | Microsoft .NET Framework | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Minitab | Node.js | نرم‌افزار محیط توسعه شیءگرا | Oracle Java | PTC Creo Parametric | Perl | Portalgraphics openCanvas | Python | نرم‌افزار SAP | نرم‌افزار Salesforce | Selenium | Siemens NX | Siemens Solid Edge | Siemens Teamcenter | Somat eDAQ | نرم‌افزار تحلیل آماری | زبان پرس‌وجوی ساختاریافته SQL | Swift | SystemVerilog | TestNG | The MathWorks MATLAB | Think3 ThinkDesign Engineering | UNIX | زبان توصیف سخت‌افزار مدار مجتمع با سرعت بسیار بالا VHSIC VHDL | Xcode</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نوشتن | صحبت کردن | ریاضیات | گوش دادن فعال | یادگیری فعال | علوم | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,17 +746,17 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | خلاقیت | استدلال ریاضی | بیان نوشتاری | تجسم | دید نزدیک | تشخیص گفتار | وضوح گفتار | نظم‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | اصالت | استدلال ریاضی | بیان کتبی | تجسم | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا صحیح بودن | محیط داخلی، دارای کنترل محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | ارتباط با دیگران | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | سطح رقابت | سلامت و ایمنی سایر کارگران</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | اهمیت دقیق یا درست بودن | محیط داخلی، دارای کنترل شرایط محیطی | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | صرف زمان برای نشستن | فشار زمانی | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | سطح رقابت | سلامت و ایمنی سایر کارکنان</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>تکنولوژیست‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مکانیک‌ها و تکنسین‌های سرویس خودرو | تکنسین‌های اویونیک | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنولوژیست‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران برق و الکترونیک، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز رایانه | مهندسان پیل سوختی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنولوژیست‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
+          <t>تکنسین‌ها و کارشناسان مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های هوانوردی | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | تعمیرکنندگان تجهیزات الکتریکی و الکترونیکی، تجهیزات تجاری و صنعتی | مهندسان الکترونیک، به جز کامپیوتر | مهندسان پیل سوختی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | تکنسین‌ها و کارشناسان مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,12 +788,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | برنامه‌های نرم‌افزاری تجاری | Carlson SurvCADD | نرم‌افزار طراحی و نقشه‌کشی به کمک رایانه CADD | CyberArk | GEO-SLOPE GeoStudio | Gemcom PCBC | Gemcom Surpac | Gemcom Whittle | سیستم‌های سیستم اطلاعات جغرافیایی GIS | GijimaAst Mining Solutions International Mine2-4D | Hellman &amp; Schofield MP3 | Maptek Vulcan | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Mincom MineScape | MineSight | Minemax iGantt | Modular Mining Systems DISPATCH | MySQL | Ohio Automation Integrated Computer Aided Mine Planning System ICAMPS | Oracle Database | Oracle JD Edwards EnterpriseOne | Oracle Primavera Systems | Overland Conveyor Belt Analyst | Promine | RungePincockMinarco XERAS | RungePincockMinarco XPAC | نرم‌افزار SAP | Schlumberger PIPESIM | نرم‌افزار نقشه‌برداری سایت | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Trimble Geomatics Office | VMware | Ventsim</t>
+          <t>Autodesk AutoCAD | Autodesk AutoCAD Civil 3D | Bentley MicroStation | برنامه‌های نرم‌افزاری تجاری | Carlson SurvCADD | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | CyberArk | GEO-SLOPE GeoStudio | Gemcom PCBC | Gemcom Surpac | Gemcom Whittle | سیستم‌های سیستم اطلاعات جغرافیایی GIS | GijimaAst Mining Solutions International Mine2-4D | Hellman &amp; Schofield MP3 | Maptek Vulcan | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft Project | Microsoft SharePoint | Microsoft Windows | Microsoft Word | Mincom MineScape | MineSight | Minemax iGantt | Modular Mining Systems DISPATCH | MySQL | Ohio Automation Integrated Computer Aided Mine Planning System ICAMPS | Oracle Database | Oracle JD Edwards EnterpriseOne | Oracle Primavera Systems | Overland Conveyor Belt Analyst | Promine | RungePincockMinarco XERAS | RungePincockMinarco XPAC | نرم‌افزار SAP | Schlumberger PIPESIM | نرم‌افزار نقشه‌برداری سایت | نرم‌افزار آماری | زبان پرس‌وجوی ساختاریافته SQL | Trimble Geomatics Office | VMware | Ventsim</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | صحبت کردن | نوشتن | درک مطلب | گوش دادن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری دسته‌بندی | درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | دید نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | خلاقیت | توانایی عددی | توجه انتخابی | تجسم | دید دور | سرعت ادراکی | سرعت بستار</t>
+          <t>انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توانایی عددی | توجه انتخابی | تجسم | بینایی دور | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | بحث‌های حضوری با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | نامه‌ها و یادداشت‌های نوشتاری | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | فرکانس تصمیم‌گیری | فشار زمانی | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | محیط داخلی، دارای کنترل شرایط محیطی | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | نامه‌ها و یادداشت‌های کتبی | ارتباط با دیگران | تأثیر تصمیمات بر همکاران یا نتایج شرکت | صرف زمان برای نشستن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فراوانی تصمیم‌گیری | فشار زمانی | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | تکنولوژیست‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | اپراتورهای ماشین‌آلات معدن پیوسته | حفاران زمین، به جز نفت و گاز | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارگران مواد منفجره، متخصصان جابجایی مهمات و انفجار | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | دانشمندان علوم زمین، به جز هیدرولوژیست‌ها و جغرافیدانان | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مواد | مهندسان هسته‌ای | مهندسان نفت | مهندسان آب/فاضلاب</t>
+          <t>مهندسان شیمی | تکنسین‌ها و کارشناسان مهندسی عمران | مهندسان عمران | مدیران ساخت‌وساز | اپراتورهای ماشین استخراج مداوم | حفاران زمین، به جز نفت و گاز | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | کارگران مواد منفجره، متخصصان جابجایی مهمات و آتشبارها | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | زمین‌شناسان، به‌جز آب‌شناسان و جغرافی‌دانان | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مواد | مهندسان هسته‌ای | مهندسان نفت | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>کد رایانه‌ای ارزیابی دوز ANISN | نرم‌افزار شبیه‌سازی ANSYS | کدهای حمل‌ونقل هسته‌ای BERMUDA | C++ | کدهای ارزیابی دوز Discrete ordinates DORT | کد FOLLOW | زبان برنامه‌نویسی FORTRAN | نرم‌افزار گرافیکی | کد INCORE | Linux | کد ارزیابی دوز MCNP | کدهای ارزیابی دوز MERCURE | کد ارزیابی دوز MORSE-CG | Maplesoft Maple | نرم‌افزار شبیه‌سازی ریاضی | Mathsoft Mathcad | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار شبیه‌سازی مونت کارلو | Oracle Java | نرم‌افزار ارزیابی ریسک احتمالی PRA | Python | کد محافظ QAD | برنامه تحلیل و خروج رآکتور RELAP | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | SAS | کد تخلیه نقطه و واپاشی SCALE ORIGEN-S | نرم‌افزار Salesforce | Scientech Safety Monitor | Scientech WinNUPRA | ابزارهای توسعه نرم‌افزار | کد TOTE | The MathWorks MATLAB | کد تحلیل رآکتور گذرا TRAC | UNIX</t>
+          <t>کد رایانه‌ای ارزیابی دوز ANISN | نرم‌افزار شبیه‌سازی ANSYS | کدهای حمل‌ونقل هسته‌ای BERMUDA | C++ | کدهای ارزیابی دوز Discrete ordinates DORT | کد FOLLOW | Formula translation/translator FORTRAN | نرم‌افزار گرافیکی | کد INCORE | Linux | کد ارزیابی دوز MCNP | کدهای ارزیابی دوز MERCURE | کد ارزیابی دوز MORSE-CG | Maplesoft Maple | نرم‌افزار شبیه‌سازی ریاضی | Mathsoft Mathcad | Microsoft Access | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Word | نرم‌افزار شبیه‌سازی مونت کارلو | Oracle Java | نرم‌افزار ارزیابی ریسک احتمالی PRA | Python | کد محافظ QAD | برنامه تحلیل و خروج رآکتور RELAP | نرم‌افزار پایگاه داده رابطه‌ای | نرم‌افزار SAP | SAS | کد تخلیه نقطه و واپاشی SCALE ORIGEN-S | نرم‌افزار Salesforce | Scientech Safety Monitor | Scientech WinNUPRA | ابزارهای توسعه نرم‌افزار | کد TOTE | The MathWorks MATLAB | کد تحلیل رآکتور گذرا TRAC | UNIX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نوشتن | گوش دادن فعال | درک مطلب | یادگیری فعال | صحبت کردن | استراتژی‌های یادگیری</t>
+          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,17 +860,17 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | درک نوشتاری | بیان شفاهی | دید نزدیک | توانایی عددی | درک شنیداری | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | خلاقیت | سرعت ادراکی | تجسم | توجه انتخابی | دید دور</t>
+          <t>حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | درک کتبی | بیان شفاهی | بینایی نزدیک | توانایی عددی | درک شفاهی | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | اصالت | سرعت ادراکی | تجسم | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | اهمیت دقیق یا صحیح بودن | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | سلامت و ایمنی سایر کارگران | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | پیامد خطا | فشار زمانی | قرار گرفتن در معرض تابش | نامه‌ها و یادداشت‌های نوشتاری</t>
+          <t>ایمیل | اهمیت دقیق یا درست بودن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | سلامت و ایمنی سایر کارکنان | کار با یا مشارکت در یک گروه کاری یا تیم | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | پیامد خطا | فشار زمانی | قرار گرفتن در معرض تابش | نامه‌ها و یادداشت‌های کتبی</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران فناوری سوخت‌های زیستی/بیودیزل و توسعه محصول | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان شیمی | مهندسان انرژی، به جز باد و خورشید | تکنولوژیست‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علوم محیطی و حفاظتی، شامل بهداشت | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | تکنولوژیست‌های مهندسی نانوتکنولوژی | تکنسین‌های نظارت هسته‌ای | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای نیروگاه</t>
+          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به جز باد و خورشید | تکنسین‌ها و کارشناسان مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های علم و حفاظت محیط زیست، شامل بهداشت | مهندسان پیل سوختی | مدیران تولید زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | تکنسین‌ها و کارشناسان مهندسی نانوتکنولوژی | تکنسین‌های نظارت هسته‌ای | اپراتورهای راکتور قدرت هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای نیروگاه برق</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نوشتن | صحبت کردن | یادگیری فعال | نظارت | علوم | ریاضیات | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -917,17 +917,17 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک نوشتاری | بیان شفاهی | بیان نوشتاری | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شنیداری | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | نظم‌دهی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | خلاقیت | تجسم | استدلال ریاضی | توجه انتخابی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | اصالت | تجسم | استدلال ریاضی | توجه انتخابی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>بحث‌های حضوری با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل محیطی | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فرکانس تصمیم‌گیری | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارگران | فشار زمانی | سلامت و ایمنی سایر کارگران | سطح رقابت</t>
+          <t>گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ایمیل | کار با یا مشارکت در یک گروه کاری یا تیم | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | محیط داخلی، دارای کنترل شرایط محیطی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای نشستن | تأثیر تصمیمات بر همکاران یا نتایج شرکت | آزادی در تصمیم‌گیری | فراوانی تصمیم‌گیری | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | فشار زمانی | سلامت و ایمنی سایر کارکنان | سطح رقابت</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران فناوری سوخت‌های زیستی/بیودیزل و توسعه محصول | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | مهندسان محیط زیست | اپراتورهای کارخانه گاز | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنولوژیست‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | اپراتورهای سیستم پمپ نفت، اپراتورهای پالایشگاه و اندازه‌گیرها | اپراتورهای واحد خدمات، نفت و گاز | اپراتورهای کارخانه و سیستم تصفیه آب و فاضلاب | مهندسان آب/فاضلاب | پمپ‌زن‌های سرچاه</t>
+          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان انرژی، به جز باد و خورشید | مهندسان محیط زیست | اپراتورهای واحدهای گاز | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | تکنسین‌ها و کارشناسان مهندسی صنایع | مهندسان صنایع | مهندسان تولید | مهندسان مکانیک | مهندسان معدن و زمین‌شناسی، شامل مهندسان ایمنی معدن | اپراتورهای سامانه پمپ نفت، اپراتورهای پالایشگاه و متصدیان اندازه‌گیری | اپراتورهای واحد خدمات، نفت و گاز | اپراتورهای سیستم و تصفیه‌خانه آب و فاضلاب | مهندسان آب و فاضلاب | پمپ‌کنندگان سرچاهی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,12 +959,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی به کمک رایانه سه‌بعدی 3D | نرم‌افزار طراحی به کمک رایانه دوبعدی 2D | نرم‌افزار ایمیل | Microsoft PowerPoint | Python | Microsoft Access</t>
+          <t>Autodesk AutoCAD | Dassault Systemes SolidWorks | PTC Creo Parametric | Siemens NX | نرم‌افزار شبیه‌سازی ANSYS | Bentley MicroStation | The MathWorks MATLAB | Microsoft Excel | Microsoft Word | Microsoft Project | نرم‌افزار طراحی سه بعدی به کمک کامپیوتر CAD | نرم‌افزار طراحی دو بعدی به کمک کامپیوتر CAD | نرم‌افزار ایمیل | Microsoft PowerPoint | Python | Microsoft Access</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نوشتن | صحبت کردن | گوش دادن فعال | علوم | نظارت | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -974,17 +974,17 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شنیداری | درک نوشتاری | بیان شفاهی | بیان نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | خلاقیت | توجه انتخابی | اشتراک زمانی | تجسم | حافظه‌سپاری | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | بحث‌های حضوری با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | فشار زمانی | نامه‌ها و یادداشت‌های نوشتاری | فرکانس تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | برخورد با مشتریان خارجی یا عموم مردم | هماهنگی یا رهبری دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل محیطی | پیامد خطا | سلامت و ایمنی سایر کارگران | پوشیدن تجهیزات حفاظتی یا ایمنی رایج مانند کفش ایمنی، عینک، دستکش، محافظ شنوایی، کلاه ایمنی یا جلیقه نجات</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | محیط داخلی، بدون کنترل شرایط محیطی | پیامد خطا | سلامت و ایمنی سایر کارکنان | استفاده از تجهیزات حفاظتی یا ایمنی معمول مانند کفش ایمنی، عینک، دستکش، محافظ گوش، کلاه ایمنی یا جلیقه نجات</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان انرژی، به جز باد و خورشید | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان فوتونیک | مهندسان رباتیک | مهندسان نانوسیستم | مهندسان انرژی باد | مهندسان سیستم‌های انرژی خورشیدی | مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان الکترونیک، به جز رایانه | مهندسان صنایع | مهندسان مواد | مهندسان مکانیک | مهندسان هسته‌ای | مهندسان محیط زیست | مهندسان سخت‌افزار رایانه | مدیران معماری و مهندسی</t>
+          <t>مهندسان انرژی، به جز باد و خورشید | مهندسان مکاترونیک | مهندسان میکروسیستم | مهندسان فوتونیک | مهندسان رباتیک | مهندسان نانوسیستم | مهندسان انرژی بادی | مهندسان سیستم‌های انرژی خورشیدی | مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | مهندسان مواد | مهندسان مکانیک | مهندسان هسته‌ای | مهندسان محیط زیست | مهندسان سخت‌افزار کامپیوتر | مدیران معماری و مهندسی</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | نوشتن | صحبت کردن | ریاضیات | یادگیری فعال | علوم</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1031,17 +1031,17 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شنیداری | درک نوشتاری | استدلال قیاسی | استدلال استقرایی | نظم‌دهی اطلاعات | استدلال ریاضی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | بیان نوشتاری | انعطاف‌پذیری دسته‌بندی | تجسم | توجه انتخابی | خلاقیت | توانایی عددی | روانی ایده‌ها | دید دور | انعطاف‌پذیری بستار</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تجسم | توجه انتخابی | اصالت | توانایی عددی | روانی ایده‌ها | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل محیطی | بحث‌های حضوری با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا صحیح بودن | نتایج کاری و خروجی‌های سایر کارگران | برخورد با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن</t>
+          <t>ایمیل | مکالمات تلفنی | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | پیامدهای کاری و نتایج سایر کارکنان | تعامل با مشتریان خارجی یا عموم مردم | صرف زمان برای نشستن</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران فناوری سوخت‌های زیستی/بیودیزل و توسعه محصول | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان برق | ممیزان انرژی | مهندسان محیط زیست | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصاب‌های گرمایش، تهویه مطبوع و تبرید | مدیران تولید برق‌آبی | مهندسان مکانیک | توزیع‌کنندگان و دیسپاچرهای برق | اپراتورهای نیروگاه | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نمایندگان فروش و ارزیابان خورشیدی | نصاب‌ها و تکنسین‌های حرارتی خورشیدی | مهندسان آب/فاضلاب | مدیران توسعه انرژی باد | مهندسان انرژی باد</t>
+          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی/بیودیزل | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | بازرسان انرژی | مهندسان محیط زیست | مدیران تولید زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان گرمایش، تهویه مطبوع و تبرید | مدیران تولید برق‌آبی | مهندسان مکانیک | توزیع‌کنندگان و دیسپچرهای برق | اپراتورهای نیروگاه برق | مدیران نصب انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | نمایندگان و ارزیابان فروش تجهیزات خورشیدی | نصابان و تکنسین‌های حرارتی خورشیدی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0018_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0018_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | علوم | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | مکانیک | طراحی | زبان انگلیسی | ترابری | ریاضیات | فیزیک | ساختمان و سازه | رایانه و الکترونیک | آموزش و پرورش | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | مکانیک | طراحی | زبان انگلیسی | حمل و نقل | ریاضیات | فیزیک | ساختمان و ساخت‌وساز | رایانه و الکترونیک | آموزش و پرورش | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | تجسم فضایی | ابتکار | دید نزدیک | وضوح گفتار | انعطاف‌پذیری در ادراک الگو | روانی کلام و ایده | تشخیص گفتار | دید دور | توانایی کار با اعداد | توجه انتخابی | سرعت در ادراک الگو | تشخیص رنگ‌ها | سرعت ادراک</t>
+          <t>استدلال قیاسی | بیان کتبی | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | درک شفاهی | درک کتبی | بیان شفاهی | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | تجسم | اصالت | بینایی نزدیک | وضوح گفتار | انعطاف‌پذیری بستار | روانی ایده‌ها | تشخیص گفتار | بینایی دور | توانایی عددی | توجه انتخابی | سرعت بستار | تشخیص رنگ بصری | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | مکانیک‌ها و تعمیرکاران هواپیما | مونتاژکاران سازه، سطوح، اتصالات و سامانه‌های هوایی | مدیران معماری و مهندسی | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک هوانوردی | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | تکنسین‌های الکترومکانیک و مکاترونیک | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان صنایع | کارگران تعمیر و نگهداری عمومی | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مکانیک‌ها و تعمیرکاران قایق‌های موتوری | مهندسان کشتی و موتورخانه</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | مکانیک و تکنسین خدمات هواپیما | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مدیران فنی و مهندسی و معماری | تکنسین‌های مهندسی خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان صنایع | کارگران عمومی تعمیرات و نگهداری تاسیسات | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مکانیک و تکنسین شناورهای موتوری | مهندسان فنی کشتی</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>علوم | شنیدن فعال | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
+          <t>علوم | گوش دادن فعال | درک مطلب | تفکر انتقادی | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | تولید و فرآوری | زبان انگلیسی | طراحی | رایانه و الکترونیک | مکانیک | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>مهندسی و فناوری | شیمی | فیزیک | ریاضیات | تولید و فرآوری | زبان انگلیسی | طراحی | رایانه و الکترونیک | مکانیک | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری در طبقه‌بندی | بیان کتبی | حساسیت به مسئله | دید نزدیک | مرتب‌سازی اطلاعات | استدلال ریاضی | روانی کلام و ایده | ابتکار | انعطاف‌پذیری در ادراک الگو | سرعت ادراک | تجسم فضایی | تشخیص گفتار | وضوح گفتار | توانایی کار با اعداد | توجه انتخابی | تشخیص رنگ‌ها</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | انعطاف‌پذیری دسته‌بندی | بیان کتبی | حساسیت به مسئله | بینایی نزدیک | ترتیب‌دهی اطلاعات | استدلال ریاضی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار | سرعت ادراکی | تجسم | تشخیص گفتار | وضوح گفتار | توانایی عددی | توجه انتخابی | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مدیران معماری و مهندسی | مهندسان زیست‌پزشکی و بیوالکتریک | مهندسان شیمی | تکنسین‌های شیمی | شیمیدانان | طراحان تجاری و صنعتی | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک (به‌جز کامپیوتر) | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | دانشمندان علم مواد | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو | مهندسان نانوسامانه‌ها | کاردان‌ها و تکنسین‌های مهندسی فناوری نانو | تکنسین‌های فوتونیک</t>
+          <t>مدیران فنی و مهندسی و معماری | مهندسان پزشکی و بیوانجینیرینگ | مهندسان شیمی | تکنسین‌های شیمی | شیمی‌دانان | طراحان تجاری و صنعتی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های فوتونیک و اپتیک</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>درک مطلب | شنیدن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نگارش | سخن گفتن | نظارت</t>
+          <t>درک مطلب | گوش دادن فعال | تفکر انتقادی | ریاضیات | علوم | یادگیری فعال | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>طراحی | مهندسی و فناوری | تولید و فرآوری | مکانیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | فیزیک | امور اداری | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی</t>
+          <t>طراحی | مهندسی و فناوری | تولید و فرآوری | مکانیک | زبان انگلیسی | ریاضیات | ایمنی و امنیت عمومی | رایانه و الکترونیک | آموزش و پرورش | فیزیک | اداری | مدیریت و اداره | خدمات مشتری و شخصی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | مرتب‌سازی اطلاعات | استدلال ریاضی | دید نزدیک | بیان کتبی | توانایی کار با اعداد | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | تجسم فضایی | ابتکار | انعطاف‌پذیری در ادراک الگو | تشخیص گفتار | وضوح گفتار | به‌خاطرسپاری | توجه انتخابی | سرعت ادراک</t>
+          <t>استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بینایی نزدیک | بیان کتبی | توانایی عددی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | تجسم | اصالت | انعطاف‌پذیری بستار | تشخیص گفتار | وضوح گفتار | حفظ کردن | توجه انتخابی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا | مونتاژکاران سازه، سطوح، اتصالات و سامانه‌های هوایی | مهندسان خودرو | کاردان‌ها و تکنسین‌های کالیبراسیون | نصابان و تعمیرکاران کنترل و شیرآلات (به‌جز درب‌های مکانیکی) | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات برقی و الکترونیکی | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک (به‌جز کامپیوتر) | مونتاژکاران موتور و سایر ماشین‌آلات صنعتی | مهندسان پیل سوختی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان ساخت و تولید | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | مهندسان تأسیسات و اپراتورهای دیگ بخار</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مونتاژکاران سازه، سطوح، مهاربندی و سیستم‌های هواپیما | مهندسان خودرو | تکنسین‌ها و کارشناسان فنی کالیبراسیون | نصابان و تعمیرکاران شیرآلات صنعتی و تجهیزات کنترلی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مونتاژکاران تجهیزات الکتریکی و الکترونیکی | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مونتاژکاران تجهیزات الکترومکانیکی | مهندسان الکترونیک، به‌جز کامپیوتر | مونتاژکاران موتور و سایر ماشین‌آلات | مهندسان پیل سوختی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مکانیک‌های ماشین‌آلات صنعتی | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکاترونیک | مهندسان تأسیسات و اپراتورهای دیگ‌بخار صنعتی</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | علوم | نگارش | سخن گفتن | شنیدن فعال | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | علوم | نگارش | سخن گفتن | گوش دادن فعال | یادگیری فعال | نظارت | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | دید نزدیک | روانی کلام و ایده | ابتکار | توجه انتخابی | انعطاف‌پذیری در ادراک الگو | تشخیص گفتار | توانایی کار با اعداد | تجسم فضایی | دید دور | وضوح گفتار | سرعت در ادراک الگو | سرعت ادراک</t>
+          <t>بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | درک کتبی | بیان شفاهی | استدلال ریاضی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | بینایی نزدیک | روانی ایده‌ها | اصالت | توجه انتخابی | انعطاف‌پذیری بستار | تشخیص گفتار | توانایی عددی | تجسم | بینایی دور | وضوح گفتار | سرعت بستار | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | مدیران توسعه محصول و فناوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک (به‌جز کامپیوتر) | مهندسان انرژی (به‌جز بادی و خورشیدی) | دانشمندان علم مواد | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو | مهندسان نانوسامانه‌ها | مهندسان هسته‌ای | مهندسان سامانه‌های خورشیدی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مهندسان خودرو | مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مهندسان شیمی | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | کارشناسان و تکنسین‌های الکترومکانیک و مکاترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان انرژی، به‌جز بادی و خورشیدی | کارشناسان و دانشمندان علوم مواد | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان نانوسیستم‌ها | مهندسان هسته‌ای | مهندسان سیستم‌های انرژی خورشیدی</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,17 +736,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | شنیدن فعال | یادگیری فعال | علوم | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | گوش دادن فعال | یادگیری فعال | علوم | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | ریاضیات | مکانیک | طراحی | رایانه و الکترونیک | ترابری | زبان انگلیسی | تولید و فرآوری | مدیریت و امور اداری | شیمی</t>
+          <t>مهندسی و فناوری | فیزیک | ریاضیات | مکانیک | طراحی | رایانه و الکترونیک | حمل و نقل | زبان انگلیسی | تولید و فرآوری | مدیریت و اداره | شیمی</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی کلام و ایده | ابتکار | استدلال ریاضی | بیان کتبی | تجسم فضایی | دید نزدیک | تشخیص گفتار | وضوح گفتار | مرتب‌سازی اطلاعات | توانایی کار با اعداد | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | دید دور</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | روانی ایده‌ها | اصالت | استدلال ریاضی | بیان کتبی | تجسم | بینایی نزدیک | تشخیص گفتار | وضوح گفتار | ترتیب‌دهی اطلاعات | توانایی عددی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>کاردان‌ها و تکنسین‌های مهندسی هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | تکنسین‌ها و مکانیک‌های خدمات خودرو | تکنسین‌های اویونیک و الکترونیک هوانوردی | کاردان‌ها و تکنسین‌های کالیبراسیون | مهندسان برق | کاردان‌ها و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکاران تجهیزات برقی و الکترونیکی تجاری و صنعتی | مهندسان الکترونیک (به‌جز کامپیوتر) | مهندسان پیل سوختی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | کاردان‌ها و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک | مهندسان صحه‌گذاری و اعتبارسنجی</t>
+          <t>کارشناسان و تکنسین‌های مهندسی و عملیات هوافضا | مهندسان هوافضا | تکنسین‌های مهندسی خودرو | مکانیک و تکنسین خدمات خودرو | تکنسین‌های اویونیک و الکترونیک پرواز | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان برق | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | تعمیرکار تجهیزات الکتریکی و الکترونیکی صنعتی و تجاری | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان پیل سوختی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | کارشناسان و تکنسین‌های مهندسی مکانیک | مهندسان مکانیک | مهندسان مکاترونیک | مهندسان رباتیک | تکنسین‌های رباتیک | مهندسان اعتبارسنجی و صحه‌گذاری</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | شنیدن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | سخن گفتن | نگارش | درک مطلب | گوش دادن فعال | ریاضیات | نظارت | علوم | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | طراحی | تولید و فرآوری | مدیریت و امور اداری | امور اداری | فیزیک | اقتصاد و حسابداری | رایانه و الکترونیک</t>
+          <t>مهندسی و فناوری | ریاضیات | زبان انگلیسی | طراحی | تولید و فرآوری | مدیریت و اداره | اداری | فیزیک | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>انعطاف‌پذیری در طبقه‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | دید نزدیک | روانی کلام و ایده | انعطاف‌پذیری در ادراک الگو | ابتکار | توانایی کار با اعداد | توجه انتخابی | تجسم فضایی | دید دور | سرعت ادراک | سرعت در ادراک الگو</t>
+          <t>انعطاف‌پذیری دسته‌بندی | درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | تشخیص گفتار | وضوح گفتار | استدلال ریاضی | بینایی نزدیک | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت | توانایی عددی | توجه انتخابی | تجسم | بینایی دور | سرعت ادراکی | سرعت بستار</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان شیمی | کاردان‌ها و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های عمرانی و ساختمانی | اپراتورهای ماشین‌آلات حفاری مداوم معدن | حفاران زمین (به‌جز نفت و گاز) | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | کارشناسان مواد منفجره، مهمات و آتشباری | تکنسین‌های زمین‌شناسی (به‌جز هیدرولوژی) | دانشمندان علوم زمین (به‌جز هیدرولوژیست‌ها و جغرافیدانان) | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان متالورژی و مواد | مهندسان هسته‌ای | مهندسان نفت | مهندسان آب و فاضلاب</t>
+          <t>مهندسان شیمی | کارشناسان و تکنسین‌های مهندسی عمران | مهندسان عمران | مدیران پروژه‌های ساختمانی | اپراتورهای ماشین‌های استخراج پیوسته | حفاران زمین، به‌جز نفت و گاز | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | کارشناسان مواد منفجره و آتش‌باری | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | زمین‌شناسان به استثنای آب‌زمین‌شناسان و جغرافیدانان | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان متالورژی و مواد | مهندسان هسته‌ای | مهندسان نفت | مهندسان آب و فاضلاب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,17 +850,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نگارش | شنیدن فعال | درک مطلب | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
+          <t>علوم | تفکر انتقادی | نظارت | ریاضیات | نگارش | گوش دادن فعال | درک مطلب | یادگیری فعال | سخن گفتن | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | فیزیک | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک | طراحی | مکانیک | آموزش و پرورش | مدیریت و امور اداری | حقوق و امور دولتی | ساختمان و سازه</t>
+          <t>مهندسی و فناوری | فیزیک | ریاضیات | زبان انگلیسی | ایمنی و امنیت عمومی | شیمی | رایانه و الکترونیک | طراحی | مکانیک | آموزش و پرورش | مدیریت و اداره | قانون و دولت | ساختمان و ساخت‌وساز</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال ریاضی | درک کتبی | بیان شفاهی | دید نزدیک | توانایی کار با اعداد | درک شفاهی | روانی کلام و ایده | وضوح گفتار | انعطاف‌پذیری در ادراک الگو | تشخیص گفتار | ابتکار | سرعت ادراک | تجسم فضایی | توجه انتخابی | دید دور</t>
+          <t>حساسیت به مسئله | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال ریاضی | درک کتبی | بیان شفاهی | بینایی نزدیک | توانایی عددی | درک شفاهی | روانی ایده‌ها | وضوح گفتار | انعطاف‌پذیری بستار | تشخیص گفتار | اصالت | سرعت ادراکی | تجسم | توجه انتخابی | بینایی دور</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان شیمی | مهندسان انرژی (به‌جز بادی و خورشیدی) | کاردان‌ها و تکنسین‌های مهندسی محیط زیست | مهندسان محیط زیست | تکنسین‌های حفاظت و علوم محیط زیست شامل بهداشت | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برق‌آبی | مدیران تولید برق‌آبی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | کاردان‌ها و تکنسین‌های مهندسی فناوری نانو | تکنسین‌های پایش پرتوی هسته‌ای | اپراتورهای راکتور نیروگاه اتمی | تکنسین‌های هسته‌ای | اپراتورهای نیروگاه برق</t>
+          <t>مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان شیمی | مهندسان انرژی، به‌جز بادی و خورشیدی | کارشناسان و تکنسین‌های مهندسی محیط زیست | مهندسان محیط‌زیست | تکنسین‌های علوم و بهداشت محیط زیست | مهندسان پیل سوختی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های نیروگاه برقابی | مدیران تولید نیروگاه‌های برق‌آبی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | کارشناسان و تکنسین‌های مهندسی نانوتکنولوژی | تکنسین‌های پایش و حفاظت پرتوی | اپراتورهای رآکتور نیروگاه هسته‌ای | تکنسین‌های هسته‌ای | اپراتورهای نیروگاه برق</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | ریاضیات | راهبردهای یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نگارش | سخن گفتن | یادگیری فعال | نظارت | علوم | ریاضیات | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | شیمی | مدیریت و امور اداری | اقتصاد و حسابداری | امور اداری | زبان انگلیسی | حقوق و امور دولتی | طراحی</t>
+          <t>مهندسی و فناوری | ریاضیات | فیزیک | رایانه و الکترونیک | شیمی | مدیریت و اداره | اقتصاد و حسابداری | اداری | زبان انگلیسی | قانون و دولت | طراحی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | مرتب‌سازی اطلاعات | دید نزدیک | وضوح گفتار | تشخیص گفتار | ابتکار | تجسم فضایی | استدلال ریاضی | توجه انتخابی | توانایی کار با اعداد | سرعت ادراک | انعطاف‌پذیری در ادراک الگو</t>
+          <t>درک کتبی | بیان شفاهی | بیان کتبی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | درک شفاهی | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | ترتیب‌دهی اطلاعات | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | اصالت | تجسم | استدلال ریاضی | توجه انتخابی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان انرژی (به‌جز بادی و خورشیدی) | مهندسان محیط زیست | اپراتورهای پالایشگاه و تأسیسات گاز | تکنسین‌های زمین‌شناسی (به‌جز هیدرولوژی) | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | کاردان‌ها و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان ساخت و تولید | مهندسان مکانیک | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | متصدیان سامانه‌های پمپاژ نفت، اپراتورهای پالایشگاه و اندازه‌گیران مخازن نفت | اپراتورهای تجهیزات خدمات چاه‌های نفت و گاز | اپراتورهای تصفیه‌خانه و شبکه‌های توزیع آب و فاضلاب | مهندسان آب و فاضلاب | متصدیان پمپ‌های سرچاهی</t>
+          <t>مدیران توسعه محصول و فناوری زیست‌سوخت | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان محیط‌زیست | اپراتورهای تأسیسات و پالایشگاه‌های گاز | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | کارشناسان و تکنسین‌های مهندسی صنایع | مهندسان صنایع | مهندسان تولید و ساخت | مهندسان مکانیک | مهندسان معدن و زمین‌شناسی شامل مهندسان ایمنی معدن | اپراتورهای پمپ‌های انتقال نفت، پالایشگاه و متصدیان اندازه‌گیری مخازن | اپراتورهای واحدهای خدمات چاه نفت و گاز | اپراتورهای تصفیه‌خانه و شبکه‌های انتقال آب و فاضلاب | مهندسان آب و فاضلاب | اپراتورهای پمپ سرچاهی نفت و گاز</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | شنیدن فعال | علوم | نظارت | راهبردهای یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | ریاضیات | یادگیری فعال | نگارش | سخن گفتن | گوش دادن فعال | علوم | نظارت | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | فیزیک | طراحی | رایانه و الکترونیک | زبان انگلیسی | مکانیک | تولید و فرآوری | مدیریت و امور اداری | شیمی</t>
+          <t>مهندسی و فناوری | ریاضیات | فیزیک | طراحی | رایانه و الکترونیک | زبان انگلیسی | مکانیک | تولید و فرآوری | مدیریت و اداره | شیمی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی کلام و ایده | ابتکار | توجه انتخابی | اشتراک زمانی | تجسم فضایی | به‌خاطرسپاری | استدلال ریاضی | توانایی کار با اعداد | سرعت ادراک | انعطاف‌پذیری در ادراک الگو | ثبات دست و بازو | چابکی انگشتان</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | ثبات دست و بازو | مهارت انگشتان</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان انرژی (به‌جز بادی و خورشیدی) | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو | مهندسان فوتونیک | مهندسان رباتیک | مهندسان نانوسامانه‌ها | مهندسان انرژی بادی | مهندسان سامانه‌های خورشیدی | مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان الکترونیک (به‌جز کامپیوتر) | مهندسان صنایع | مهندسان متالورژی و مواد | مهندسان مکانیک | مهندسان هسته‌ای | مهندسان محیط زیست | مهندسان سخت‌افزار کامپیوتر | مدیران معماری و مهندسی</t>
+          <t>مهندسان انرژی، به‌جز بادی و خورشیدی | مهندسان مکاترونیک | مهندسان سامانه‌های میکرو / میکروسیستم‌ها | مهندسان فوتونیک | مهندسان رباتیک | مهندسان نانوسیستم‌ها | مهندسان انرژی باد | مهندسان سیستم‌های انرژی خورشیدی | مهندسان هوافضا | مهندسان شیمی | مهندسان عمران | مهندسان برق | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان صنایع | مهندسان متالورژی و مواد | مهندسان مکانیک | مهندسان هسته‌ای | مهندسان محیط‌زیست | مهندسان سخت‌افزار رایانه | مدیران فنی و مهندسی و معماری</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | علوم</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | علوم</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>مهندسی و فناوری | ریاضیات | ساختمان و سازه | خدمات مشتریان و خدمات فردی | مکانیک | زبان انگلیسی | مدیریت و امور اداری | طراحی | فیزیک | اقتصاد و حسابداری | رایانه و الکترونیک</t>
+          <t>مهندسی و فناوری | ریاضیات | ساختمان و ساخت‌وساز | خدمات مشتری و شخصی | مکانیک | زبان انگلیسی | مدیریت و اداره | طراحی | فیزیک | اقتصاد و حسابداری | رایانه و الکترونیک</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | استدلال ریاضی | بیان شفاهی | وضوح گفتار | دید نزدیک | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | تجسم فضایی | توجه انتخابی | ابتکار | توانایی کار با اعداد | روانی کلام و ایده | دید دور | انعطاف‌پذیری در ادراک الگو</t>
+          <t>حساسیت به مسئله | درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | استدلال ریاضی | بیان شفاهی | وضوح گفتار | بینایی نزدیک | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | تجسم | توجه انتخابی | اصالت | توانایی عددی | روانی ایده‌ها | بینایی دور | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>مدیران توسعه محصول و فناوری سوخت‌های زیستی | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه زیست‌توده | مهندسان برق | ممیزان انرژی | مهندسان محیط زیست | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های زمین‌گرمایی | مکانیک‌ها و نصابان تأسیسات گرمایشی، تهویه مطبوع و برودتی | مدیران تولید برق‌آبی | مهندسان مکانیک | توزیع‌کنندگان و دیسپاچرهای شبکه برق | اپراتورهای نیروگاه برق | مدیران اجرای تأسیسات انرژی خورشیدی | مهندسان سامانه‌های خورشیدی | کارشناسان فروش و ارزیابان انرژی خورشیدی | نصابان و تکنسین‌های سامانه‌های خورشیدی حرارتی | مهندسان آب و فاضلاب | مدیران توسعه انرژی بادی | مهندسان انرژی بادی</t>
+          <t>مدیران توسعه محصول و فناوری زیست‌سوخت | تکنسین‌های نیروگاه زیست‌توده | مدیران نیروگاه‌های زیست‌توده | مهندسان برق | ممیزان انرژی | مهندسان محیط‌زیست | مدیران تولید انرژی زمین‌گرمایی | تکنسین‌های سامانه‌های زمین‌گرمایی | مکانیک‌ها و نصابان سیستم‌های گرمایشی، تهویه مطبوع و تبرید | مدیران تولید نیروگاه‌های برق‌آبی | مهندسان مکانیک | دیسپچرها و توزیع‌کنندگان شبکه برق | اپراتورهای نیروگاه برق | مدیران اجرای پروژه‌های انرژی خورشیدی | مهندسان سیستم‌های انرژی خورشیدی | کارشناسان فروش و ارزیابان سامانه‌های خورشیدی | نصابان و تکنسین‌های سیستم‌های خورشیدی حرارتی | مهندسان آب و فاضلاب | مدیران توسعه پروژه‌های انرژی بادی | مهندسان انرژی باد</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
